--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574015763</v>
+        <v>46157.93116001246</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116001246</v>
+        <v>46157.93182296058</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93182296058</v>
+        <v>46157.93405287711</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405287711</v>
+        <v>46157.93723371792</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723371792</v>
+        <v>46158.28221183105</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221183105</v>
+        <v>46158.29701189653</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701189653</v>
+        <v>46158.29820875941</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820875941</v>
+        <v>46158.3339222393</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339222393</v>
+        <v>46158.36861981846</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861981846</v>
+        <v>46158.37292730584</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
